--- a/backend/data/financials_by_company/1I4.F.xlsx
+++ b/backend/data/financials_by_company/1I4.F.xlsx
@@ -3603,10 +3603,8 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3123</t>
-        </is>
+      <c r="E2" t="n">
+        <v>3123</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3814,7 +3812,7 @@
         <v>-4131627</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
         <v>52.3</v>
@@ -4027,7 +4025,7 @@
         <v>258.3333</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DS2" t="n">
         <v>-0.003659999</v>
